--- a/output/pdf_financials_xlsx/TLP.UN.xlsx
+++ b/output/pdf_financials_xlsx/TLP.UN.xlsx
@@ -1074,13 +1074,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.468122</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.150368</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.352579</v>
       </c>
     </row>
     <row r="35">
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.468122</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.150368</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.352579</v>
       </c>
     </row>
     <row r="37">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">

--- a/output/pdf_financials_xlsx/TLP.UN.xlsx
+++ b/output/pdf_financials_xlsx/TLP.UN.xlsx
@@ -2259,13 +2259,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0</v>
+        <v>-0.078986</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0</v>
+        <v>0.004762</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0</v>
+        <v>0.007653</v>
       </c>
     </row>
     <row r="107">
@@ -3950,7 +3950,11 @@
           <t>Net change in non-cash balances related to operations</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E43" s="5" t="n">
         <v>-0.078986</v>
       </c>
